--- a/spravki/spravka_rnntd_quarter_2026-09-30.xlsx
+++ b/spravki/spravka_rnntd_quarter_2026-09-30.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>64.9 млрд ₸</t>
+          <t>65.7 млрд ₸</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 407. Сформировано 16.10.2026.</t>
+          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 475. Сформировано 16.10.2026.</t>
         </is>
       </c>
     </row>
